--- a/was/xlsx/vtnode_build_myapp/vtnode_ui_only.xlsx
+++ b/was/xlsx/vtnode_build_myapp/vtnode_ui_only.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\vtnode\was\xlsx\vtnode_build_myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD7BBDBB-4AB1-442D-8782-D5B767B9951D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7177F011-08DE-4CE1-A2CB-BB910F283E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25950" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MyApp" sheetId="1" r:id="rId1"/>
+    <sheet name="VTNode Hello" sheetId="1" r:id="rId1"/>
     <sheet name="_README" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -332,6 +332,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -364,9 +370,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -384,9 +387,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -718,38 +718,38 @@
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="14"/>
     </row>
     <row r="4" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="11"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
@@ -772,30 +772,30 @@
       <c r="I7" s="7"/>
     </row>
     <row r="8" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="22" t="s">
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="20" t="s">
+      <c r="F8" s="27"/>
+      <c r="G8" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
     </row>
     <row r="10" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="5"/>
@@ -808,38 +808,38 @@
       <c r="I10" s="7"/>
     </row>
     <row r="11" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="12" t="s">
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="11"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="14"/>
     </row>
     <row r="13" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="15"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="17"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
@@ -852,38 +852,38 @@
       <c r="I14" s="7"/>
     </row>
     <row r="15" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="29" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="30"/>
+      <c r="I15" s="31"/>
     </row>
     <row r="16" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="14"/>
       <c r="E16" s="36"/>
       <c r="F16" s="37"/>
       <c r="G16" s="37"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="17" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="35"/>
     </row>
     <row r="18" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
